--- a/data/predictions/2026-04-29_HV.xlsx
+++ b/data/predictions/2026-04-29_HV.xlsx
@@ -539,12 +539,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -556,8 +560,10 @@
           <t>FAMILY FORTUNE</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>8</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -574,47 +580,79 @@
           <t>1/5/7/5/9/1</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>9.608695652173912</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6.7863</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.4</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.67</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>9.608695652173912</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>6.7863</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -626,8 +664,10 @@
           <t>PERFECT PEACH</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -644,47 +684,79 @@
           <t>10/10/13/2/1/7</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7.652173913043478</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6.7763</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.4</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7.652173913043478</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6.7763</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -696,8 +768,10 @@
           <t>CELESTIAL HARMONY</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>7</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -714,47 +788,79 @@
           <t>4/6/1/12/14/3</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6.6305</v>
-      </c>
-      <c r="R4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.3</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6.6305</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -766,8 +872,10 @@
           <t>PERFECT PAIRING</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>5</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -784,47 +892,79 @@
           <t>7/3/12/6/8/2</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>8.043478260869566</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.502</v>
-      </c>
-      <c r="R5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7.1</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>8.043478260869566</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>6.502</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -836,8 +976,10 @@
           <t>THE PERFECT MATCH</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>7</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -854,47 +996,79 @@
           <t>9/7/4/3/2/2</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.9765</v>
-      </c>
-      <c r="R6" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6.9765</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -906,8 +1080,10 @@
           <t>KING GLORIOSO</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -924,47 +1100,79 @@
           <t>6/4/5/4/1/6</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6.4595</v>
-      </c>
-      <c r="R7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6.4</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>6.4595</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -976,8 +1184,10 @@
           <t>HONEST WITNESS</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>4</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -994,47 +1204,79 @@
           <t>1/8/11/5/2/11</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.212</v>
-      </c>
-      <c r="R8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8.300000000000001</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>6.212</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1046,8 +1288,10 @@
           <t>VERY GRATEFUL</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1064,47 +1308,79 @@
           <t>10/4/11/11/6/4</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.156</v>
-      </c>
-      <c r="R9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8.800000000000001</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>6.156</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1116,8 +1392,10 @@
           <t>NOBLE PURSUIT</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>3</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1134,47 +1412,79 @@
           <t>4/9/9/2/6/5</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.7093</v>
-      </c>
-      <c r="R10" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.1</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8.875</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.7093</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1186,8 +1496,10 @@
           <t>SERANGOON</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1204,47 +1516,79 @@
           <t>6/7/1/12/4/7</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8.3125</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.5971</v>
-      </c>
-      <c r="R11" t="n">
-        <v>15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.7</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8.3125</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>6.5971</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1256,8 +1600,10 @@
           <t>OCEAN IMPACT</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1274,47 +1620,79 @@
           <t>9/11/10/4/6/1</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4.9375</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.3789</v>
-      </c>
-      <c r="R12" t="n">
-        <v>12</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7.1</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4.9375</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>6.3789</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1326,8 +1704,10 @@
           <t>DOUBLE WIN</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>7</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1344,47 +1724,79 @@
           <t>5/3/10/6/9/1</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.3208</v>
-      </c>
-      <c r="R13" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>7.5</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6.625</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>6.3208</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1396,8 +1808,10 @@
           <t>CROSSBORDERDUDE</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>5</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1414,47 +1828,79 @@
           <t>3/3/2/1/3/3</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>7.8485</v>
-      </c>
-      <c r="R14" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.9</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>7.8485</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1466,8 +1912,10 @@
           <t>ACE POWER</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1484,47 +1932,79 @@
           <t>6/2/5/3/3/10</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.263157894736842</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6.5307</v>
-      </c>
-      <c r="R15" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5.263157894736842</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6.5307</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1536,8 +2016,10 @@
           <t>FIND MY LOVE</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1554,47 +2036,79 @@
           <t>6/8/4/6/7/5</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7.157894736842105</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.3225</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>8.6</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>7.157894736842105</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6.3225</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1606,8 +2120,10 @@
           <t>JOY CAPITAL</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>9</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1624,47 +2140,79 @@
           <t>10/9/8/1/11</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>8.105263157894736</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.9552</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S17" t="n">
-        <v>12.5</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>8.105263157894736</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.9552</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1676,8 +2224,10 @@
           <t>SUPERB KING</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>6</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1694,47 +2244,79 @@
           <t>3/2/8/10/2/4</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>9.526315789473685</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.8494</v>
-      </c>
-      <c r="R18" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>9.526315789473685</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6.8494</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1746,8 +2328,10 @@
           <t>THUNDER PRINCE</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>8</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1764,47 +2348,79 @@
           <t>1/8/4/5/3/4</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.4724</v>
-      </c>
-      <c r="R19" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.4</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6.4724</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1816,8 +2432,10 @@
           <t>GAMEPLAYER ELITE</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1834,47 +2452,79 @@
           <t>2/1/5/3/10/8</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5.263157894736842</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.2157</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>7</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>5.263157894736842</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6.2157</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1886,8 +2536,10 @@
           <t>LEGEND STAR</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1904,47 +2556,79 @@
           <t>7/1/14/1/9/5</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.315789473684211</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.1736</v>
-      </c>
-      <c r="R21" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7.3</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4.315789473684211</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6.1736</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1956,8 +2640,10 @@
           <t>BEAUTY VIVA</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>3</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1974,47 +2660,79 @@
           <t>7/1/9/5/9/2</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.714285714285715</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.8444</v>
-      </c>
-      <c r="R22" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>8.714285714285715</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.8444</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2026,8 +2744,10 @@
           <t>MIGHTY STEED</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>12</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2044,47 +2764,79 @@
           <t>2/5/7/7/3/3</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.755</v>
-      </c>
-      <c r="R23" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.4</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6.755</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2096,8 +2848,10 @@
           <t>NEVER TOO SOON</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>2</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2114,47 +2868,79 @@
           <t>7/9/4/4/6/6</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7.428571428571429</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.4447</v>
-      </c>
-      <c r="R24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>7.4</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7.428571428571429</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>6.4447</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2166,8 +2952,10 @@
           <t>THE ABSOLUTE</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>11</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2184,47 +2972,79 @@
           <t>8/9/7/3/4/3</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>7.428571428571429</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>6.4282</v>
-      </c>
-      <c r="R25" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>7.5</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>7.428571428571429</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6.4282</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2236,8 +3056,10 @@
           <t>COLOURFUL KING</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>5</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2254,47 +3076,79 @@
           <t>6/6/2/2/1/2</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="K26" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>8.333333333333332</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>7.6435</v>
-      </c>
-      <c r="R26" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>8.333333333333332</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7.6435</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>33.5</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2306,8 +3160,10 @@
           <t>STELLAR EXPRESS</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>9</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2324,47 +3180,79 @@
           <t>7/6/1/1/1/14</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>10</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7.0385</v>
-      </c>
-      <c r="R27" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.6</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>7.0385</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2376,8 +3264,10 @@
           <t>GLOWING PRAISES</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>8</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2394,47 +3284,79 @@
           <t>2/3/5/1</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.465</v>
-      </c>
-      <c r="R28" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8.300000000000001</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.666666666666667</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>6.465</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2446,8 +3368,10 @@
           <t>BRAVE STAR</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>3</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2464,47 +3388,79 @@
           <t>2/3/3/14/1/9</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.3035</v>
-      </c>
-      <c r="R29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S29" t="n">
-        <v>9.699999999999999</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6.3035</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,8 +3472,10 @@
           <t>HAPPY INDEX</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>12</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2534,47 +3492,79 @@
           <t>3/2/1/3</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7.448</v>
-      </c>
-      <c r="R30" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.7</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>7.448</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2586,8 +3576,10 @@
           <t>MID WINTER WIND</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>7</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2604,47 +3596,79 @@
           <t>7/3/4/3/12/3</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="K31" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>10</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.9305</v>
-      </c>
-      <c r="R31" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6.2</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6.9305</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2656,8 +3680,10 @@
           <t>GIANT BALLON</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>6</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2674,47 +3700,79 @@
           <t>1/1/5/3/4/2</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="K32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>6.8975</v>
-      </c>
-      <c r="R32" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>6.3</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>7.67</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6.8975</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2726,8 +3784,10 @@
           <t>SPORTS LEGEND</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>2</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2744,47 +3804,79 @@
           <t>5/9/2/5/1/7</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6.6935</v>
-      </c>
-      <c r="R33" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S33" t="n">
-        <v>7.8</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>6.6935</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2796,8 +3888,10 @@
           <t>CORLEONE</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>8</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2814,47 +3908,79 @@
           <t>8/1/2/1/1/5</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="K34" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>8.411764705882353</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7.3435</v>
-      </c>
-      <c r="R34" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.2</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>8.411764705882353</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7.3435</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2866,8 +3992,10 @@
           <t>SOLID WIN</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>9</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2884,47 +4012,79 @@
           <t>4/1/7/1/9/6</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="K35" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>10</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.6395</v>
-      </c>
-      <c r="R35" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6.5</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.6395</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2936,8 +4096,10 @@
           <t>KEEFY</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>10</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2954,47 +4116,79 @@
           <t>4/2/3/4/5/9</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="K36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>9.470588235294118</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.5182</v>
-      </c>
-      <c r="R36" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S36" t="n">
-        <v>7.3</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>9.470588235294118</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>6.5182</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3006,8 +4200,10 @@
           <t>CALIFORNIA MOXIE</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>11</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3024,39 +4220,67 @@
           <t>10/6/1/7/3/1</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.117647058823529</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6.2398</v>
-      </c>
-      <c r="R37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S37" t="n">
-        <v>9.699999999999999</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>3.117647058823529</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>6.2398</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +4459,6 @@
           <t>3/2/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -3316,7 +4539,6 @@
           <t>7/3/4/3/12/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.81</v>
       </c>
@@ -3397,7 +4619,6 @@
           <t>1/1/5/3/4/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.67</v>
       </c>
@@ -3478,7 +4699,6 @@
           <t>5/9/2/5/1/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.9</v>
       </c>
@@ -3644,7 +4864,6 @@
           <t>8/1/5/9/1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.33</v>
       </c>
@@ -3810,7 +5029,6 @@
           <t>4/5/2/4/5/4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>6.1</v>
       </c>
@@ -3891,7 +5109,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -3972,7 +5189,6 @@
           <t>8/8/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.5</v>
       </c>
@@ -4053,7 +5269,6 @@
           <t>12/8/1/11/13/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.38</v>
       </c>
@@ -4134,7 +5349,6 @@
           <t>7/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.67</v>
       </c>
@@ -4346,7 +5560,6 @@
           <t>8/1/2/1/1/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.050000000000001</v>
       </c>
@@ -4427,7 +5640,6 @@
           <t>4/1/7/1/9/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.19</v>
       </c>
@@ -4508,7 +5720,6 @@
           <t>4/2/3/4/5/9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.19</v>
       </c>
@@ -4589,7 +5800,6 @@
           <t>10/6/1/7/3/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.19</v>
       </c>
@@ -4670,7 +5880,6 @@
           <t>4/6/1/1/1/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.95</v>
       </c>
@@ -4751,7 +5960,6 @@
           <t>8/9/9/2/4/12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4</v>
       </c>
@@ -4832,7 +6040,6 @@
           <t>1/2/5/5/8/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.33</v>
       </c>
@@ -4913,7 +6120,6 @@
           <t>3/7/5/3/3/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.1</v>
       </c>
@@ -4994,7 +6200,6 @@
           <t>3/1/7/10/4/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.95</v>
       </c>
@@ -5075,7 +6280,6 @@
           <t>10/11/13/11/8/6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.1</v>
       </c>
@@ -5156,7 +6360,6 @@
           <t>7/6/8/8/1/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>4.14</v>
       </c>
@@ -5237,7 +6440,6 @@
           <t>11/10/8/8/10/5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.48</v>
       </c>
@@ -5422,7 +6624,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>5</t>
@@ -5524,7 +6725,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>6</t>
@@ -5626,7 +6826,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2</t>
@@ -5728,7 +6927,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
@@ -5830,7 +7028,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2</t>
@@ -5932,7 +7129,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>3</t>
@@ -6034,7 +7230,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>2</t>
@@ -6136,7 +7331,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>2</t>
@@ -6238,7 +7432,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>3</t>
@@ -6513,7 +7706,6 @@
           <t>1/5/7/5/9/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.67</v>
       </c>
@@ -6594,7 +7786,6 @@
           <t>10/10/13/2/1/7</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.24</v>
       </c>
@@ -6675,7 +7866,6 @@
           <t>4/6/1/12/14/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.81</v>
       </c>
@@ -6756,7 +7946,6 @@
           <t>7/3/12/6/8/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.86</v>
       </c>
@@ -6837,7 +8026,6 @@
           <t>7/9/8/9/13/4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2.95</v>
       </c>
@@ -6918,7 +8106,6 @@
           <t>4/10/9/7/2/7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.24</v>
       </c>
@@ -6999,7 +8186,6 @@
           <t>9/6/6/3/9/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.62</v>
       </c>
@@ -7080,7 +8266,6 @@
           <t>7/8/13/9/11/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.38</v>
       </c>
@@ -7161,7 +8346,6 @@
           <t>12/6/13/12/9/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.81</v>
       </c>
@@ -7242,7 +8426,6 @@
           <t>7/10/10/7/10/6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.33</v>
       </c>
@@ -7323,7 +8506,6 @@
           <t>11/9/9/11/10/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.52</v>
       </c>
@@ -7404,7 +8586,6 @@
           <t>6/8/13/13/7/7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.29</v>
       </c>
@@ -7616,7 +8797,6 @@
           <t>9/7/4/3/2/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.48</v>
       </c>
@@ -7697,7 +8877,6 @@
           <t>6/4/5/4/1/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.14</v>
       </c>
@@ -7778,7 +8957,6 @@
           <t>1/8/11/5/2/11</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.19</v>
       </c>
@@ -7859,7 +9037,6 @@
           <t>10/4/11/11/6/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.62</v>
       </c>
@@ -7940,7 +9117,6 @@
           <t>7/12/3/11/7/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.14</v>
       </c>
@@ -8021,7 +9197,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -8102,7 +9277,6 @@
           <t>6/4/10/9/6/1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.1</v>
       </c>
@@ -8183,7 +9357,6 @@
           <t>8/11/4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.67</v>
       </c>
@@ -8264,7 +9437,6 @@
           <t>10/13/13/10/7/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.33</v>
       </c>
@@ -8345,7 +9517,6 @@
           <t>9/10/7/10/11/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.33</v>
       </c>
@@ -8426,7 +9597,6 @@
           <t>8/14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.33</v>
       </c>
@@ -8507,7 +9677,6 @@
           <t>8/8/10/7/9/7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.33</v>
       </c>
@@ -8719,7 +9888,6 @@
           <t>4/9/9/2/6/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>4.86</v>
       </c>
@@ -8800,7 +9968,6 @@
           <t>6/7/1/12/4/7</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>4.38</v>
       </c>
@@ -8881,7 +10048,6 @@
           <t>9/11/10/4/6/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.29</v>
       </c>
@@ -8962,7 +10128,6 @@
           <t>5/3/10/6/9/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.24</v>
       </c>
@@ -9043,7 +10208,6 @@
           <t>3/2/5/9/1/5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.14</v>
       </c>
@@ -9124,7 +10288,6 @@
           <t>8/3/7/3/12/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.19</v>
       </c>
@@ -9205,7 +10368,6 @@
           <t>4/9/5/6/9/10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.71</v>
       </c>
@@ -9286,7 +10448,6 @@
           <t>3/2/2/2/2/8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>6.95</v>
       </c>
@@ -9367,7 +10528,6 @@
           <t>6/3/4/3/4/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5.05</v>
       </c>
@@ -9448,7 +10608,6 @@
           <t>12/12/11/12/11/14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
       </c>
@@ -9529,7 +10688,6 @@
           <t>1/12/11/11/12/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
@@ -9610,7 +10768,6 @@
           <t>6/14/6/13/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.8</v>
       </c>
@@ -9822,7 +10979,6 @@
           <t>3/3/2/1/3/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.52</v>
       </c>
@@ -9903,7 +11059,6 @@
           <t>6/2/5/3/3/10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.48</v>
       </c>
@@ -9984,7 +11139,6 @@
           <t>6/8/4/6/7/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.14</v>
       </c>
@@ -10065,7 +11219,6 @@
           <t>10/9/8/1/11</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.73</v>
       </c>
@@ -10146,7 +11299,6 @@
           <t>12/11/8/4/12/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.67</v>
       </c>
@@ -10227,7 +11379,6 @@
           <t>2/9/4/8/12/9</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.67</v>
       </c>
@@ -10308,7 +11459,6 @@
           <t>9/11/5/10/1/12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.76</v>
       </c>
@@ -10389,7 +11539,6 @@
           <t>8/8/9/11/12/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.29</v>
       </c>
@@ -10555,7 +11704,6 @@
           <t>6/11/9/7/4/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.86</v>
       </c>
@@ -10636,7 +11784,6 @@
           <t>12/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.67</v>
       </c>
@@ -10933,7 +12080,6 @@
           <t>3/2/8/10/2/4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.57</v>
       </c>
@@ -11014,7 +12160,6 @@
           <t>1/8/4/5/3/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.1</v>
       </c>
@@ -11095,7 +12240,6 @@
           <t>2/1/5/3/10/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.43</v>
       </c>
@@ -11176,7 +12320,6 @@
           <t>7/1/14/1/9/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.05</v>
       </c>
@@ -11257,7 +12400,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -11338,7 +12480,6 @@
           <t>8/7/11/12/12/11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>1.24</v>
       </c>
@@ -11419,7 +12560,6 @@
           <t>9/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
@@ -11500,7 +12640,6 @@
           <t>10/11/8/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.3</v>
       </c>
@@ -11581,7 +12720,6 @@
           <t>8/13/10/13/13/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.33</v>
       </c>
@@ -11662,7 +12800,6 @@
           <t>7/12/7/7/11/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.76</v>
       </c>
@@ -11743,7 +12880,6 @@
           <t>13/12/8/8/11/6</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.19</v>
       </c>
@@ -11824,7 +12960,6 @@
           <t>13/13/6/10/7/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.19</v>
       </c>
@@ -12036,7 +13171,6 @@
           <t>7/1/9/5/9/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.38</v>
       </c>
@@ -12117,7 +13251,6 @@
           <t>2/5/7/7/3/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.1</v>
       </c>
@@ -12198,7 +13331,6 @@
           <t>7/9/4/4/6/6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.43</v>
       </c>
@@ -12279,7 +13411,6 @@
           <t>8/9/7/3/4/3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.95</v>
       </c>
@@ -12360,7 +13491,6 @@
           <t>4/9/8/6/5/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.86</v>
       </c>
@@ -12441,7 +13571,6 @@
           <t>2/4/2/2/8/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.19</v>
       </c>
@@ -12522,7 +13651,6 @@
           <t>5/3/9/8/10/11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.19</v>
       </c>
@@ -12603,7 +13731,6 @@
           <t>11/9/6/11/6/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
@@ -12684,7 +13811,6 @@
           <t>1/8/6/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3</v>
       </c>
@@ -12765,7 +13891,6 @@
           <t>11/3/9/6/6/3</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.1</v>
       </c>
@@ -12846,7 +13971,6 @@
           <t>11/9/9/13/12/14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.24</v>
       </c>
@@ -12927,7 +14051,6 @@
           <t>5/2/8/6/11/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.67</v>
       </c>
@@ -13139,7 +14262,6 @@
           <t>6/6/2/2/1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.52</v>
       </c>
@@ -13220,7 +14342,6 @@
           <t>7/6/1/1/1/14</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.52</v>
       </c>
@@ -13301,7 +14422,6 @@
           <t>2/3/5/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>8</v>
       </c>
@@ -13552,7 +14672,6 @@
           <t>4/7/6/13/7/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.48</v>
       </c>
@@ -13633,7 +14752,6 @@
           <t>8/9/5/5/10/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.62</v>
       </c>
@@ -13799,7 +14917,6 @@
           <t>5/6/5/6/8/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.14</v>
       </c>
@@ -13880,7 +14997,6 @@
           <t>5/10/6/6/8/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.71</v>
       </c>
